--- a/_诊断_修复后_特殊示例_2.xlsx
+++ b/_诊断_修复后_特殊示例_2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="29865" windowHeight="15255" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="总表" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="101">
   <si>
     <t>统计表</t>
   </si>
@@ -65,34 +65,223 @@
     <t>例6</t>
   </si>
   <si>
+    <t>期望</t>
+  </si>
+  <si>
+    <t>哇哇哇</t>
+  </si>
+  <si>
+    <t>发给还是电饭锅</t>
+  </si>
+  <si>
+    <t>而感到十分</t>
+  </si>
+  <si>
+    <t>变成v女</t>
+  </si>
+  <si>
+    <t>vnydj</t>
+  </si>
+  <si>
+    <t>是第几份工那就让</t>
+  </si>
+  <si>
+    <t>都是不尴尬</t>
+  </si>
+  <si>
+    <t>按时发工资啊的</t>
+  </si>
+  <si>
+    <t>等复刻啥破公开怕</t>
+  </si>
+  <si>
+    <t>爱的放</t>
+  </si>
+  <si>
+    <t>上课都发高烧平底锅</t>
+  </si>
+  <si>
+    <t>时空的皮肤顾客排水管</t>
+  </si>
+  <si>
+    <t>师傅干活</t>
+  </si>
+  <si>
+    <t>记得发好贵啊是</t>
+  </si>
+  <si>
+    <t>啊地方不爱你的发</t>
+  </si>
+  <si>
+    <t>是的平方根破地方</t>
+  </si>
+  <si>
+    <t>啊代购阿道夫</t>
+  </si>
+  <si>
+    <t>欧派多少个富婆</t>
+  </si>
+  <si>
+    <t>阿道夫就更加</t>
+  </si>
+  <si>
+    <t>开始破洞裤分工平时</t>
+  </si>
+  <si>
+    <t>手机都附近公司</t>
+  </si>
+  <si>
+    <t>水电费告诉对方</t>
+  </si>
+  <si>
+    <t>对方过后电饭锅</t>
+  </si>
+  <si>
+    <t>收到苹果放假人</t>
+  </si>
+  <si>
+    <t>水电费那个就是</t>
+  </si>
+  <si>
+    <t>是的平均分狗平安京PDF</t>
+  </si>
+  <si>
+    <t>时代峰峻告诉对方</t>
+  </si>
+  <si>
+    <t>跟你打算佛一觉睡到</t>
+  </si>
+  <si>
+    <t>手机对哦给送</t>
+  </si>
+  <si>
+    <t>手机关机送</t>
+  </si>
+  <si>
+    <t>开公司的放狗屁上课的皮肤</t>
+  </si>
+  <si>
+    <t>爱上对方</t>
+  </si>
+  <si>
+    <t>宿舍的方式sdfgsd</t>
+  </si>
+  <si>
+    <t>发的刚好风格和</t>
+  </si>
+  <si>
+    <t>俺弟</t>
+  </si>
+  <si>
+    <t>阿萨打算的</t>
+  </si>
+  <si>
+    <t>的风格的</t>
+  </si>
+  <si>
+    <t>二手房是</t>
+  </si>
+  <si>
+    <t>二月十四下个班</t>
+  </si>
+  <si>
+    <t>水电费估计是啊大哥了</t>
+  </si>
+  <si>
+    <t>骄傲来得及发过来</t>
+  </si>
+  <si>
+    <t>的飞机票告诉发给</t>
+  </si>
+  <si>
+    <t>拒收到付件欧冠</t>
+  </si>
+  <si>
+    <t>公司的分公司</t>
+  </si>
+  <si>
+    <t>交水电费dss</t>
+  </si>
+  <si>
+    <t>特价的风格</t>
+  </si>
+  <si>
+    <t xml:space="preserve">是都发过来可爱； </t>
+  </si>
+  <si>
+    <t>爱的借口发个好看的</t>
+  </si>
+  <si>
+    <t>手机都尬死的</t>
+  </si>
+  <si>
+    <t>是的减肥公司</t>
+  </si>
+  <si>
+    <t>SOIDJFIOG</t>
+  </si>
+  <si>
+    <t>爱多分股票a</t>
+  </si>
+  <si>
+    <t>是的分公司的</t>
+  </si>
+  <si>
+    <t>安静地欧公安</t>
+  </si>
+  <si>
+    <t>谁的关爱</t>
+  </si>
+  <si>
+    <t>会员积分兑换</t>
+  </si>
+  <si>
+    <t>是的发给老师；dklf</t>
+  </si>
+  <si>
+    <t>俺回家上课讲的</t>
+  </si>
+  <si>
+    <t>啊收到苹果恐怕开始地方</t>
+  </si>
+  <si>
+    <t>啊佛国记</t>
+  </si>
+  <si>
+    <t>求带飞公安</t>
+  </si>
+  <si>
+    <t>io放假狗ID</t>
+  </si>
+  <si>
+    <t>感受到公司发给</t>
+  </si>
+  <si>
+    <t>手机豆腐干送</t>
+  </si>
+  <si>
+    <t>谁的风格</t>
+  </si>
+  <si>
+    <t>对方过后水电费</t>
+  </si>
+  <si>
+    <t>要求表</t>
+  </si>
+  <si>
+    <t>填报说明：1.</t>
+  </si>
+  <si>
+    <t>填报单位（盖章）：</t>
+  </si>
+  <si>
+    <t>QQQ</t>
+  </si>
+  <si>
+    <t>例XXX</t>
+  </si>
+  <si>
     <t>AAA</t>
-  </si>
-  <si>
-    <t>XXXAAA</t>
-  </si>
-  <si>
-    <t>XXXAAAAAA</t>
-  </si>
-  <si>
-    <t>AAAAAA</t>
-  </si>
-  <si>
-    <t>XXAAA</t>
-  </si>
-  <si>
-    <t>要求表</t>
-  </si>
-  <si>
-    <t>填报说明：1.</t>
-  </si>
-  <si>
-    <t>填报单位（盖章）：</t>
-  </si>
-  <si>
-    <t>QQQ</t>
-  </si>
-  <si>
-    <t>例XXX</t>
   </si>
   <si>
     <t>SSS</t>
@@ -159,7 +348,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="33">
+  <fonts count="32">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -178,13 +367,6 @@
       <color rgb="FF000000"/>
       <name val="黑体"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
@@ -592,7 +774,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="24">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -789,10 +971,85 @@
         <color rgb="FF000000"/>
       </left>
       <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
         <color rgb="FF000000"/>
       </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD9D9D9"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -911,265 +1168,274 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="21" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="16" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="4" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="5" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="6" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="4" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="25" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="24" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="26" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="27" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="28" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1657,59 +1923,59 @@
       <c r="A6" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="31">
+      <c r="B6" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C6" s="30">
         <f>G6+G7</f>
         <v>16</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>2</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>3</v>
       </c>
-      <c r="F6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="G6" s="31">
+      <c r="F6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="G6" s="30">
         <v>1</v>
       </c>
-      <c r="H6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="I6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="J6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="K6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="L6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="M6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="N6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="O6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="P6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="R6" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="S6" s="32" t="s">
+      <c r="H6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="I6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="J6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="K6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="L6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="M6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="N6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="O6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="P6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="R6" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="S6" s="31" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1717,52 +1983,52 @@
       <c r="A7" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="30" t="s">
+      <c r="B7" s="16" t="s">
         <v>6</v>
       </c>
       <c r="C7" s="28"/>
       <c r="D7" s="28"/>
       <c r="E7" s="28"/>
-      <c r="F7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="G7" s="30">
+      <c r="F7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="G7" s="16">
         <v>15</v>
       </c>
-      <c r="H7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="I7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="J7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="K7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="L7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="M7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="N7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="O7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="P7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="R7" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="S7" s="32" t="s">
+      <c r="H7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="J7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="L7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="M7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="N7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="O7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="P7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="R7" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="S7" s="31" t="s">
         <v>6</v>
       </c>
     </row>
@@ -1770,1458 +2036,1458 @@
       <c r="A8" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="30" t="s">
-        <v>6</v>
-      </c>
-      <c r="C8" s="31">
+      <c r="B8" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="30">
         <f>G8</f>
         <v>3</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>3</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>3</v>
       </c>
-      <c r="F8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="G8" s="31">
+      <c r="F8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="30">
         <v>3</v>
       </c>
-      <c r="H8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="I8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="J8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="K8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="L8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="M8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="N8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="O8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="P8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="Q8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="R8" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="S8" s="32" t="s">
+      <c r="H8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="I8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="J8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="K8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="L8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="M8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="N8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="O8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="P8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="Q8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="R8" s="31" t="s">
+        <v>6</v>
+      </c>
+      <c r="S8" s="31" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="9" ht="59.25" customHeight="1" spans="1:19">
-      <c r="A9" s="33">
+      <c r="A9" s="32">
         <v>4</v>
       </c>
-      <c r="B9" s="34" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="35">
+      <c r="B9" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="C9" s="34">
         <v>33</v>
       </c>
-      <c r="D9" s="35"/>
-      <c r="E9" s="35"/>
-      <c r="F9" s="35"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-      <c r="K9" s="37"/>
-      <c r="L9" s="37"/>
-      <c r="M9" s="37"/>
-      <c r="N9" s="38"/>
-      <c r="O9" s="38"/>
-      <c r="P9" s="38"/>
-      <c r="Q9" s="38"/>
-      <c r="R9" s="38"/>
-      <c r="S9" s="35"/>
+      <c r="D9" s="34"/>
+      <c r="E9" s="34"/>
+      <c r="F9" s="34"/>
+      <c r="G9" s="34"/>
+      <c r="H9" s="35"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
+      <c r="M9" s="36"/>
+      <c r="N9" s="37"/>
+      <c r="O9" s="37"/>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="37"/>
+      <c r="R9" s="37"/>
+      <c r="S9" s="34"/>
     </row>
     <row r="10" ht="21" customHeight="1" spans="1:19">
-      <c r="A10" s="39">
+      <c r="A10" s="38">
         <v>5</v>
       </c>
-      <c r="B10" s="40"/>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="42"/>
-      <c r="J10" s="42"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="42"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="43"/>
-      <c r="O10" s="44"/>
-      <c r="P10" s="44"/>
-      <c r="Q10" s="44"/>
-      <c r="R10" s="44"/>
-      <c r="S10" s="41"/>
+      <c r="B10" s="39"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="40"/>
+      <c r="H10" s="41"/>
+      <c r="I10" s="41"/>
+      <c r="J10" s="41"/>
+      <c r="K10" s="41"/>
+      <c r="L10" s="41"/>
+      <c r="M10" s="41"/>
+      <c r="N10" s="42"/>
+      <c r="O10" s="43"/>
+      <c r="P10" s="43"/>
+      <c r="Q10" s="43"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="40"/>
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A11" s="45">
-        <v>6</v>
-      </c>
-      <c r="B11" s="46" t="s">
+      <c r="A11" s="44">
+        <v>6</v>
+      </c>
+      <c r="B11" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="31">
         <v>3</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="31">
         <v>42</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="31">
         <v>122</v>
       </c>
-      <c r="F11" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="G11" s="32">
+      <c r="F11" s="31" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11" s="31">
         <v>54</v>
       </c>
-      <c r="H11" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I11" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="J11" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K11" s="47" t="s">
-        <v>11</v>
+      <c r="H11" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="I11" s="31" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="31" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="46" t="s">
+        <v>15</v>
       </c>
       <c r="L11" s="47" t="s">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="M11" s="47" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N11" s="47" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="O11" s="47" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="P11" s="47" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="Q11" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="R11" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="S11" s="32"/>
+        <v>21</v>
+      </c>
+      <c r="R11" s="48" t="s">
+        <v>22</v>
+      </c>
+      <c r="S11" s="31"/>
     </row>
     <row r="12" ht="21" customHeight="1" spans="1:19">
-      <c r="A12" s="45">
+      <c r="A12" s="44">
         <v>7</v>
       </c>
-      <c r="B12" s="48"/>
-      <c r="C12" s="48"/>
-      <c r="D12" s="48"/>
-      <c r="E12" s="48"/>
-      <c r="F12" s="48"/>
-      <c r="G12" s="48"/>
-      <c r="H12" s="48"/>
+      <c r="B12" s="49"/>
+      <c r="C12" s="49"/>
+      <c r="D12" s="49"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="49"/>
+      <c r="G12" s="49"/>
+      <c r="H12" s="49"/>
       <c r="I12" s="28"/>
-      <c r="J12" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K12" s="47" t="s">
-        <v>11</v>
+      <c r="J12" s="31" t="s">
+        <v>23</v>
+      </c>
+      <c r="K12" s="46" t="s">
+        <v>24</v>
       </c>
       <c r="L12" s="47" t="s">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="M12" s="47" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="N12" s="47" t="s">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="O12" s="47" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="P12" s="47" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="Q12" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="R12" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="S12" s="32"/>
+        <v>30</v>
+      </c>
+      <c r="R12" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="S12" s="31"/>
     </row>
     <row r="13" ht="21" customHeight="1" spans="1:19">
-      <c r="A13" s="45">
+      <c r="A13" s="44">
         <v>8</v>
       </c>
-      <c r="B13" s="48"/>
-      <c r="C13" s="48"/>
-      <c r="D13" s="48"/>
-      <c r="E13" s="48"/>
+      <c r="B13" s="49"/>
+      <c r="C13" s="49"/>
+      <c r="D13" s="49"/>
+      <c r="E13" s="49"/>
       <c r="F13" s="28"/>
       <c r="G13" s="28"/>
-      <c r="H13" s="48"/>
-      <c r="I13" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="J13" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K13" s="47" t="s">
-        <v>11</v>
+      <c r="H13" s="49"/>
+      <c r="I13" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="K13" s="46" t="s">
+        <v>34</v>
       </c>
       <c r="L13" s="47" t="s">
-        <v>11</v>
+        <v>35</v>
       </c>
       <c r="M13" s="47" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="N13" s="47" t="s">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="O13" s="47" t="s">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="P13" s="47" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="Q13" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="R13" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="S13" s="32"/>
+        <v>40</v>
+      </c>
+      <c r="R13" s="48" t="s">
+        <v>41</v>
+      </c>
+      <c r="S13" s="31"/>
     </row>
     <row r="14" ht="36.75" customHeight="1" spans="1:19">
-      <c r="A14" s="45">
+      <c r="A14" s="44">
         <v>9</v>
       </c>
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
       <c r="D14" s="28"/>
       <c r="E14" s="28"/>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" s="31">
+        <v>34</v>
+      </c>
+      <c r="H14" s="28"/>
+      <c r="I14" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="J14" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="K14" s="50"/>
+      <c r="L14" s="51"/>
+      <c r="M14" s="51"/>
+      <c r="N14" s="51"/>
+      <c r="O14" s="51"/>
+      <c r="P14" s="51"/>
+      <c r="Q14" s="51"/>
+      <c r="R14" s="52"/>
+      <c r="S14" s="31"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1" spans="1:19">
+      <c r="A15" s="38">
         <v>10</v>
       </c>
-      <c r="G14" s="32">
-        <v>34</v>
-      </c>
-      <c r="H14" s="28"/>
-      <c r="I14" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="J14" s="32" t="s">
+      <c r="B15" s="45" t="s">
+        <v>45</v>
+      </c>
+      <c r="C15" s="31">
+        <v>3</v>
+      </c>
+      <c r="D15" s="31">
+        <v>42</v>
+      </c>
+      <c r="E15" s="31">
+        <v>122</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="G15" s="31">
+        <v>54</v>
+      </c>
+      <c r="H15" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="I15" s="31" t="s">
+        <v>48</v>
+      </c>
+      <c r="J15" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="K15" s="46" t="s">
+        <v>50</v>
+      </c>
+      <c r="L15" s="47" t="s">
+        <v>51</v>
+      </c>
+      <c r="M15" s="47" t="s">
+        <v>52</v>
+      </c>
+      <c r="N15" s="47" t="s">
+        <v>53</v>
+      </c>
+      <c r="O15" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="P15" s="47" t="s">
+        <v>39</v>
+      </c>
+      <c r="Q15" s="47" t="s">
+        <v>54</v>
+      </c>
+      <c r="R15" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="S15" s="31"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1" spans="1:19">
+      <c r="A16" s="38">
         <v>11</v>
       </c>
-      <c r="K14" s="32"/>
-      <c r="L14" s="32"/>
-      <c r="M14" s="32"/>
-      <c r="N14" s="30"/>
-      <c r="O14" s="30"/>
-      <c r="P14" s="30"/>
-      <c r="Q14" s="30"/>
-      <c r="R14" s="30"/>
-      <c r="S14" s="32"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A15" s="39">
-        <v>10</v>
-      </c>
-      <c r="B15" s="46" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="32">
-        <v>3</v>
-      </c>
-      <c r="D15" s="32">
-        <v>42</v>
-      </c>
-      <c r="E15" s="32">
-        <v>122</v>
-      </c>
-      <c r="F15" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15" s="32">
-        <v>54</v>
-      </c>
-      <c r="H15" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="I15" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="J15" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K15" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="L15" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="M15" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="N15" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="O15" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="P15" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q15" s="47" t="s">
+      <c r="B16" s="49"/>
+      <c r="C16" s="49"/>
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="K16" s="46" t="s">
+        <v>57</v>
+      </c>
+      <c r="L16" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16" s="47" t="s">
+        <v>59</v>
+      </c>
+      <c r="N16" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="O16" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="P16" s="47" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q16" s="47" t="s">
+        <v>63</v>
+      </c>
+      <c r="R16" s="48" t="s">
+        <v>64</v>
+      </c>
+      <c r="S16" s="31"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1" spans="1:19">
+      <c r="A17" s="38">
         <v>12</v>
       </c>
-      <c r="R15" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="S15" s="32"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A16" s="39">
-        <v>11</v>
-      </c>
-      <c r="B16" s="48"/>
-      <c r="C16" s="48"/>
-      <c r="D16" s="48"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="48"/>
-      <c r="H16" s="48"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K16" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="L16" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="M16" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="N16" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="O16" s="47" t="s">
-        <v>11</v>
-      </c>
-      <c r="P16" s="47" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q16" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="R16" s="47" t="s">
-        <v>12</v>
-      </c>
-      <c r="S16" s="32"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A17" s="39">
-        <v>12</v>
-      </c>
-      <c r="B17" s="48"/>
-      <c r="C17" s="48"/>
-      <c r="D17" s="48"/>
-      <c r="E17" s="48"/>
+      <c r="B17" s="49"/>
+      <c r="C17" s="49"/>
+      <c r="D17" s="49"/>
+      <c r="E17" s="49"/>
       <c r="F17" s="28"/>
       <c r="G17" s="28"/>
-      <c r="H17" s="48"/>
-      <c r="I17" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="J17" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K17" s="47" t="s">
-        <v>11</v>
+      <c r="H17" s="49"/>
+      <c r="I17" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="31" t="s">
+        <v>66</v>
+      </c>
+      <c r="K17" s="46" t="s">
+        <v>67</v>
       </c>
       <c r="L17" s="47" t="s">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="M17" s="47" t="s">
-        <v>11</v>
+        <v>69</v>
       </c>
       <c r="N17" s="47" t="s">
-        <v>11</v>
+        <v>70</v>
       </c>
       <c r="O17" s="47" t="s">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="P17" s="47" t="s">
-        <v>11</v>
+        <v>72</v>
       </c>
       <c r="Q17" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="R17" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="S17" s="32"/>
+        <v>73</v>
+      </c>
+      <c r="R17" s="48" t="s">
+        <v>74</v>
+      </c>
+      <c r="S17" s="31"/>
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A18" s="39">
+      <c r="A18" s="38">
         <v>13</v>
       </c>
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
       <c r="D18" s="28"/>
       <c r="E18" s="28"/>
-      <c r="F18" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="G18" s="32">
+      <c r="F18" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="31">
         <v>34</v>
       </c>
       <c r="H18" s="28"/>
-      <c r="I18" s="32" t="s">
+      <c r="I18" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="J18" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="K18" s="53"/>
+      <c r="L18" s="54"/>
+      <c r="M18" s="54"/>
+      <c r="N18" s="54"/>
+      <c r="O18" s="54"/>
+      <c r="P18" s="54"/>
+      <c r="Q18" s="54"/>
+      <c r="R18" s="55"/>
+      <c r="S18" s="31"/>
+    </row>
+    <row r="19" ht="18.75" customHeight="1" spans="1:19">
+      <c r="A19" s="38">
         <v>14</v>
       </c>
-      <c r="J18" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="30"/>
-      <c r="O18" s="30"/>
-      <c r="P18" s="30"/>
-      <c r="Q18" s="30"/>
-      <c r="R18" s="30"/>
-      <c r="S18" s="32"/>
-    </row>
-    <row r="19" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A19" s="39">
-        <v>14</v>
-      </c>
-      <c r="B19" s="49"/>
-      <c r="C19" s="50"/>
-      <c r="D19" s="50"/>
-      <c r="E19" s="50"/>
-      <c r="F19" s="50"/>
-      <c r="G19" s="50"/>
-      <c r="H19" s="36"/>
-      <c r="I19" s="36"/>
-      <c r="J19" s="36"/>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36"/>
-      <c r="N19" s="51"/>
-      <c r="O19" s="51"/>
-      <c r="P19" s="51"/>
-      <c r="Q19" s="51"/>
-      <c r="R19" s="51"/>
-      <c r="S19" s="50"/>
+      <c r="B19" s="56"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="58"/>
+      <c r="O19" s="58"/>
+      <c r="P19" s="58"/>
+      <c r="Q19" s="58"/>
+      <c r="R19" s="58"/>
+      <c r="S19" s="57"/>
     </row>
     <row r="20" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A20" s="39">
+      <c r="A20" s="38">
         <v>15</v>
       </c>
-      <c r="B20" s="49"/>
-      <c r="C20" s="50"/>
-      <c r="D20" s="50"/>
-      <c r="E20" s="50"/>
-      <c r="F20" s="50"/>
-      <c r="G20" s="50"/>
-      <c r="H20" s="36"/>
-      <c r="I20" s="36"/>
-      <c r="J20" s="36"/>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36"/>
-      <c r="N20" s="51"/>
-      <c r="O20" s="51"/>
-      <c r="P20" s="51"/>
-      <c r="Q20" s="51"/>
-      <c r="R20" s="51"/>
-      <c r="S20" s="50"/>
+      <c r="B20" s="56"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="58"/>
+      <c r="O20" s="58"/>
+      <c r="P20" s="58"/>
+      <c r="Q20" s="58"/>
+      <c r="R20" s="58"/>
+      <c r="S20" s="57"/>
     </row>
     <row r="21" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A21" s="39">
+      <c r="A21" s="38">
         <v>16</v>
       </c>
-      <c r="B21" s="49"/>
-      <c r="C21" s="50"/>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="50"/>
-      <c r="G21" s="50"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="51"/>
-      <c r="O21" s="51"/>
-      <c r="P21" s="51"/>
-      <c r="Q21" s="51"/>
-      <c r="R21" s="51"/>
-      <c r="S21" s="50"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="58"/>
+      <c r="O21" s="58"/>
+      <c r="P21" s="58"/>
+      <c r="Q21" s="58"/>
+      <c r="R21" s="58"/>
+      <c r="S21" s="57"/>
     </row>
     <row r="22" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A22" s="39">
+      <c r="A22" s="38">
         <v>17</v>
       </c>
-      <c r="B22" s="49"/>
-      <c r="C22" s="50"/>
-      <c r="D22" s="50"/>
-      <c r="E22" s="50"/>
-      <c r="F22" s="50"/>
-      <c r="G22" s="50"/>
-      <c r="H22" s="36"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36"/>
-      <c r="N22" s="51"/>
-      <c r="O22" s="51"/>
-      <c r="P22" s="51"/>
-      <c r="Q22" s="51"/>
-      <c r="R22" s="51"/>
-      <c r="S22" s="50"/>
+      <c r="B22" s="56"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="58"/>
+      <c r="O22" s="58"/>
+      <c r="P22" s="58"/>
+      <c r="Q22" s="58"/>
+      <c r="R22" s="58"/>
+      <c r="S22" s="57"/>
     </row>
     <row r="23" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A23" s="39">
+      <c r="A23" s="38">
         <v>18</v>
       </c>
-      <c r="B23" s="49"/>
-      <c r="C23" s="50"/>
-      <c r="D23" s="50"/>
-      <c r="E23" s="50"/>
-      <c r="F23" s="50"/>
-      <c r="G23" s="50"/>
-      <c r="H23" s="36"/>
-      <c r="I23" s="36"/>
-      <c r="J23" s="36"/>
-      <c r="K23" s="36"/>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="51"/>
-      <c r="O23" s="51"/>
-      <c r="P23" s="51"/>
-      <c r="Q23" s="51"/>
-      <c r="R23" s="51"/>
-      <c r="S23" s="50"/>
+      <c r="B23" s="56"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="58"/>
+      <c r="O23" s="58"/>
+      <c r="P23" s="58"/>
+      <c r="Q23" s="58"/>
+      <c r="R23" s="58"/>
+      <c r="S23" s="57"/>
     </row>
     <row r="24" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A24" s="39">
+      <c r="A24" s="38">
         <v>19</v>
       </c>
-      <c r="B24" s="49"/>
-      <c r="C24" s="50"/>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="50"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="36"/>
-      <c r="I24" s="36"/>
-      <c r="J24" s="36"/>
-      <c r="K24" s="36"/>
-      <c r="L24" s="36"/>
-      <c r="M24" s="36"/>
-      <c r="N24" s="51"/>
-      <c r="O24" s="51"/>
-      <c r="P24" s="51"/>
-      <c r="Q24" s="51"/>
-      <c r="R24" s="51"/>
-      <c r="S24" s="50"/>
+      <c r="B24" s="56"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="58"/>
+      <c r="O24" s="58"/>
+      <c r="P24" s="58"/>
+      <c r="Q24" s="58"/>
+      <c r="R24" s="58"/>
+      <c r="S24" s="57"/>
     </row>
     <row r="25" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A25" s="39">
+      <c r="A25" s="38">
         <v>20</v>
       </c>
-      <c r="B25" s="49"/>
-      <c r="C25" s="50"/>
-      <c r="D25" s="50"/>
-      <c r="E25" s="50"/>
-      <c r="F25" s="50"/>
-      <c r="G25" s="50"/>
-      <c r="H25" s="36"/>
-      <c r="I25" s="36"/>
-      <c r="J25" s="36"/>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36"/>
-      <c r="N25" s="51"/>
-      <c r="O25" s="51"/>
-      <c r="P25" s="51"/>
-      <c r="Q25" s="51"/>
-      <c r="R25" s="51"/>
-      <c r="S25" s="50"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="58"/>
+      <c r="O25" s="58"/>
+      <c r="P25" s="58"/>
+      <c r="Q25" s="58"/>
+      <c r="R25" s="58"/>
+      <c r="S25" s="57"/>
     </row>
     <row r="26" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A26" s="39">
+      <c r="A26" s="38">
         <v>21</v>
       </c>
-      <c r="B26" s="49"/>
-      <c r="C26" s="50"/>
-      <c r="D26" s="50"/>
-      <c r="E26" s="50"/>
-      <c r="F26" s="50"/>
-      <c r="G26" s="50"/>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" s="36"/>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36"/>
-      <c r="N26" s="51"/>
-      <c r="O26" s="51"/>
-      <c r="P26" s="51"/>
-      <c r="Q26" s="51"/>
-      <c r="R26" s="51"/>
-      <c r="S26" s="50"/>
+      <c r="B26" s="56"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="58"/>
+      <c r="O26" s="58"/>
+      <c r="P26" s="58"/>
+      <c r="Q26" s="58"/>
+      <c r="R26" s="58"/>
+      <c r="S26" s="57"/>
     </row>
     <row r="27" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A27" s="39">
+      <c r="A27" s="38">
         <v>22</v>
       </c>
-      <c r="B27" s="49"/>
-      <c r="C27" s="50"/>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="50"/>
-      <c r="G27" s="50"/>
-      <c r="H27" s="36"/>
-      <c r="I27" s="36"/>
-      <c r="J27" s="36"/>
-      <c r="K27" s="36"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36"/>
-      <c r="N27" s="51"/>
-      <c r="O27" s="51"/>
-      <c r="P27" s="51"/>
-      <c r="Q27" s="51"/>
-      <c r="R27" s="51"/>
-      <c r="S27" s="50"/>
+      <c r="B27" s="56"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="35"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="58"/>
+      <c r="O27" s="58"/>
+      <c r="P27" s="58"/>
+      <c r="Q27" s="58"/>
+      <c r="R27" s="58"/>
+      <c r="S27" s="57"/>
     </row>
     <row r="28" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A28" s="39">
+      <c r="A28" s="38">
         <v>23</v>
       </c>
-      <c r="B28" s="49"/>
-      <c r="C28" s="50"/>
-      <c r="D28" s="50"/>
-      <c r="E28" s="50"/>
-      <c r="F28" s="50"/>
-      <c r="G28" s="50"/>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" s="36"/>
-      <c r="K28" s="36"/>
-      <c r="L28" s="36"/>
-      <c r="M28" s="36"/>
-      <c r="N28" s="51"/>
-      <c r="O28" s="51"/>
-      <c r="P28" s="51"/>
-      <c r="Q28" s="51"/>
-      <c r="R28" s="51"/>
-      <c r="S28" s="50"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="35"/>
+      <c r="L28" s="35"/>
+      <c r="M28" s="35"/>
+      <c r="N28" s="58"/>
+      <c r="O28" s="58"/>
+      <c r="P28" s="58"/>
+      <c r="Q28" s="58"/>
+      <c r="R28" s="58"/>
+      <c r="S28" s="57"/>
     </row>
     <row r="29" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A29" s="39">
+      <c r="A29" s="38">
         <v>24</v>
       </c>
-      <c r="B29" s="49"/>
-      <c r="C29" s="50"/>
-      <c r="D29" s="50"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="50"/>
-      <c r="G29" s="50"/>
-      <c r="H29" s="36"/>
-      <c r="I29" s="36"/>
-      <c r="J29" s="36"/>
-      <c r="K29" s="36"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36"/>
-      <c r="N29" s="51"/>
-      <c r="O29" s="51"/>
-      <c r="P29" s="51"/>
-      <c r="Q29" s="51"/>
-      <c r="R29" s="51"/>
-      <c r="S29" s="50"/>
+      <c r="B29" s="56"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="35"/>
+      <c r="I29" s="35"/>
+      <c r="J29" s="35"/>
+      <c r="K29" s="35"/>
+      <c r="L29" s="35"/>
+      <c r="M29" s="35"/>
+      <c r="N29" s="58"/>
+      <c r="O29" s="58"/>
+      <c r="P29" s="58"/>
+      <c r="Q29" s="58"/>
+      <c r="R29" s="58"/>
+      <c r="S29" s="57"/>
     </row>
     <row r="30" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A30" s="39">
+      <c r="A30" s="38">
         <v>25</v>
       </c>
-      <c r="B30" s="49"/>
-      <c r="C30" s="50"/>
-      <c r="D30" s="50"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="50"/>
-      <c r="G30" s="50"/>
-      <c r="H30" s="36"/>
-      <c r="I30" s="36"/>
-      <c r="J30" s="36"/>
-      <c r="K30" s="36"/>
-      <c r="L30" s="36"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="51"/>
-      <c r="O30" s="51"/>
-      <c r="P30" s="51"/>
-      <c r="Q30" s="51"/>
-      <c r="R30" s="51"/>
-      <c r="S30" s="50"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="35"/>
+      <c r="N30" s="58"/>
+      <c r="O30" s="58"/>
+      <c r="P30" s="58"/>
+      <c r="Q30" s="58"/>
+      <c r="R30" s="58"/>
+      <c r="S30" s="57"/>
     </row>
     <row r="31" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A31" s="39">
+      <c r="A31" s="38">
         <v>26</v>
       </c>
-      <c r="B31" s="49"/>
-      <c r="C31" s="50"/>
-      <c r="D31" s="50"/>
-      <c r="E31" s="50"/>
-      <c r="F31" s="50"/>
-      <c r="G31" s="50"/>
-      <c r="H31" s="36"/>
-      <c r="I31" s="36"/>
-      <c r="J31" s="36"/>
-      <c r="K31" s="36"/>
-      <c r="L31" s="36"/>
-      <c r="M31" s="36"/>
-      <c r="N31" s="51"/>
-      <c r="O31" s="51"/>
-      <c r="P31" s="51"/>
-      <c r="Q31" s="51"/>
-      <c r="R31" s="51"/>
-      <c r="S31" s="50"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="58"/>
+      <c r="O31" s="58"/>
+      <c r="P31" s="58"/>
+      <c r="Q31" s="58"/>
+      <c r="R31" s="58"/>
+      <c r="S31" s="57"/>
     </row>
     <row r="32" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A32" s="39">
+      <c r="A32" s="38">
         <v>27</v>
       </c>
-      <c r="B32" s="49"/>
-      <c r="C32" s="50"/>
-      <c r="D32" s="50"/>
-      <c r="E32" s="50"/>
-      <c r="F32" s="50"/>
-      <c r="G32" s="50"/>
-      <c r="H32" s="36"/>
-      <c r="I32" s="36"/>
-      <c r="J32" s="36"/>
-      <c r="K32" s="36"/>
-      <c r="L32" s="36"/>
-      <c r="M32" s="36"/>
-      <c r="N32" s="51"/>
-      <c r="O32" s="51"/>
-      <c r="P32" s="51"/>
-      <c r="Q32" s="51"/>
-      <c r="R32" s="51"/>
-      <c r="S32" s="50"/>
+      <c r="B32" s="56"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="58"/>
+      <c r="O32" s="58"/>
+      <c r="P32" s="58"/>
+      <c r="Q32" s="58"/>
+      <c r="R32" s="58"/>
+      <c r="S32" s="57"/>
     </row>
     <row r="33" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A33" s="39">
+      <c r="A33" s="38">
         <v>28</v>
       </c>
-      <c r="B33" s="49"/>
-      <c r="C33" s="50"/>
-      <c r="D33" s="50"/>
-      <c r="E33" s="50"/>
-      <c r="F33" s="50"/>
-      <c r="G33" s="50"/>
-      <c r="H33" s="36"/>
-      <c r="I33" s="36"/>
-      <c r="J33" s="36"/>
-      <c r="K33" s="36"/>
-      <c r="L33" s="36"/>
-      <c r="M33" s="36"/>
-      <c r="N33" s="51"/>
-      <c r="O33" s="51"/>
-      <c r="P33" s="51"/>
-      <c r="Q33" s="51"/>
-      <c r="R33" s="51"/>
-      <c r="S33" s="50"/>
+      <c r="B33" s="56"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="58"/>
+      <c r="O33" s="58"/>
+      <c r="P33" s="58"/>
+      <c r="Q33" s="58"/>
+      <c r="R33" s="58"/>
+      <c r="S33" s="57"/>
     </row>
     <row r="34" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A34" s="39">
+      <c r="A34" s="38">
         <v>29</v>
       </c>
-      <c r="B34" s="49"/>
-      <c r="C34" s="50"/>
-      <c r="D34" s="50"/>
-      <c r="E34" s="50"/>
-      <c r="F34" s="50"/>
-      <c r="G34" s="50"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="51"/>
-      <c r="O34" s="51"/>
-      <c r="P34" s="51"/>
-      <c r="Q34" s="51"/>
-      <c r="R34" s="51"/>
-      <c r="S34" s="50"/>
+      <c r="B34" s="56"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="58"/>
+      <c r="O34" s="58"/>
+      <c r="P34" s="58"/>
+      <c r="Q34" s="58"/>
+      <c r="R34" s="58"/>
+      <c r="S34" s="57"/>
     </row>
     <row r="35" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A35" s="39">
+      <c r="A35" s="38">
         <v>30</v>
       </c>
-      <c r="B35" s="49"/>
-      <c r="C35" s="50"/>
-      <c r="D35" s="50"/>
-      <c r="E35" s="50"/>
-      <c r="F35" s="50"/>
-      <c r="G35" s="50"/>
-      <c r="H35" s="36"/>
-      <c r="I35" s="36"/>
-      <c r="J35" s="36"/>
-      <c r="K35" s="36"/>
-      <c r="L35" s="36"/>
-      <c r="M35" s="36"/>
-      <c r="N35" s="51"/>
-      <c r="O35" s="51"/>
-      <c r="P35" s="51"/>
-      <c r="Q35" s="51"/>
-      <c r="R35" s="51"/>
-      <c r="S35" s="50"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="58"/>
+      <c r="O35" s="58"/>
+      <c r="P35" s="58"/>
+      <c r="Q35" s="58"/>
+      <c r="R35" s="58"/>
+      <c r="S35" s="57"/>
     </row>
     <row r="36" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A36" s="39">
+      <c r="A36" s="38">
         <v>31</v>
       </c>
-      <c r="B36" s="49"/>
-      <c r="C36" s="50"/>
-      <c r="D36" s="50"/>
-      <c r="E36" s="50"/>
-      <c r="F36" s="50"/>
-      <c r="G36" s="50"/>
-      <c r="H36" s="36"/>
-      <c r="I36" s="36"/>
-      <c r="J36" s="36"/>
-      <c r="K36" s="36"/>
-      <c r="L36" s="36"/>
-      <c r="M36" s="36"/>
-      <c r="N36" s="51"/>
-      <c r="O36" s="51"/>
-      <c r="P36" s="51"/>
-      <c r="Q36" s="51"/>
-      <c r="R36" s="51"/>
-      <c r="S36" s="50"/>
+      <c r="B36" s="56"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="58"/>
+      <c r="O36" s="58"/>
+      <c r="P36" s="58"/>
+      <c r="Q36" s="58"/>
+      <c r="R36" s="58"/>
+      <c r="S36" s="57"/>
     </row>
     <row r="37" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A37" s="39">
+      <c r="A37" s="38">
         <v>32</v>
       </c>
-      <c r="B37" s="49"/>
-      <c r="C37" s="50"/>
-      <c r="D37" s="50"/>
-      <c r="E37" s="50"/>
-      <c r="F37" s="50"/>
-      <c r="G37" s="50"/>
-      <c r="H37" s="50"/>
-      <c r="I37" s="50"/>
-      <c r="J37" s="50"/>
-      <c r="K37" s="50"/>
-      <c r="L37" s="50"/>
-      <c r="M37" s="50"/>
-      <c r="N37" s="51"/>
-      <c r="O37" s="51"/>
-      <c r="P37" s="51"/>
-      <c r="Q37" s="51"/>
-      <c r="R37" s="51"/>
-      <c r="S37" s="50"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
+      <c r="J37" s="57"/>
+      <c r="K37" s="57"/>
+      <c r="L37" s="57"/>
+      <c r="M37" s="57"/>
+      <c r="N37" s="58"/>
+      <c r="O37" s="58"/>
+      <c r="P37" s="58"/>
+      <c r="Q37" s="58"/>
+      <c r="R37" s="58"/>
+      <c r="S37" s="57"/>
     </row>
     <row r="38" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A38" s="39">
+      <c r="A38" s="38">
         <v>33</v>
       </c>
-      <c r="B38" s="49"/>
-      <c r="C38" s="50"/>
-      <c r="D38" s="50"/>
-      <c r="E38" s="50"/>
-      <c r="F38" s="50"/>
-      <c r="G38" s="50"/>
-      <c r="H38" s="50"/>
-      <c r="I38" s="50"/>
-      <c r="J38" s="50"/>
-      <c r="K38" s="50"/>
-      <c r="L38" s="50"/>
-      <c r="M38" s="50"/>
-      <c r="N38" s="51"/>
-      <c r="O38" s="51"/>
-      <c r="P38" s="51"/>
-      <c r="Q38" s="51"/>
-      <c r="R38" s="51"/>
-      <c r="S38" s="50"/>
+      <c r="B38" s="56"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
+      <c r="J38" s="57"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="57"/>
+      <c r="M38" s="57"/>
+      <c r="N38" s="58"/>
+      <c r="O38" s="58"/>
+      <c r="P38" s="58"/>
+      <c r="Q38" s="58"/>
+      <c r="R38" s="58"/>
+      <c r="S38" s="57"/>
     </row>
     <row r="39" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A39" s="39">
+      <c r="A39" s="38">
         <v>34</v>
       </c>
-      <c r="B39" s="49"/>
-      <c r="C39" s="50"/>
-      <c r="D39" s="50"/>
-      <c r="E39" s="50"/>
-      <c r="F39" s="50"/>
-      <c r="G39" s="50"/>
-      <c r="H39" s="50"/>
-      <c r="I39" s="50"/>
-      <c r="J39" s="50"/>
-      <c r="K39" s="50"/>
-      <c r="L39" s="50"/>
-      <c r="M39" s="50"/>
-      <c r="N39" s="51"/>
-      <c r="O39" s="51"/>
-      <c r="P39" s="51"/>
-      <c r="Q39" s="51"/>
-      <c r="R39" s="51"/>
-      <c r="S39" s="50"/>
+      <c r="B39" s="56"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
+      <c r="J39" s="57"/>
+      <c r="K39" s="57"/>
+      <c r="L39" s="57"/>
+      <c r="M39" s="57"/>
+      <c r="N39" s="58"/>
+      <c r="O39" s="58"/>
+      <c r="P39" s="58"/>
+      <c r="Q39" s="58"/>
+      <c r="R39" s="58"/>
+      <c r="S39" s="57"/>
     </row>
     <row r="40" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A40" s="39">
+      <c r="A40" s="38">
         <v>35</v>
       </c>
-      <c r="B40" s="49"/>
-      <c r="C40" s="50"/>
-      <c r="D40" s="50"/>
-      <c r="E40" s="50"/>
-      <c r="F40" s="50"/>
-      <c r="G40" s="50"/>
-      <c r="H40" s="50"/>
-      <c r="I40" s="50"/>
-      <c r="J40" s="50"/>
-      <c r="K40" s="50"/>
-      <c r="L40" s="50"/>
-      <c r="M40" s="50"/>
-      <c r="N40" s="51"/>
-      <c r="O40" s="51"/>
-      <c r="P40" s="51"/>
-      <c r="Q40" s="51"/>
-      <c r="R40" s="51"/>
-      <c r="S40" s="50"/>
+      <c r="B40" s="56"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
+      <c r="J40" s="57"/>
+      <c r="K40" s="57"/>
+      <c r="L40" s="57"/>
+      <c r="M40" s="57"/>
+      <c r="N40" s="58"/>
+      <c r="O40" s="58"/>
+      <c r="P40" s="58"/>
+      <c r="Q40" s="58"/>
+      <c r="R40" s="58"/>
+      <c r="S40" s="57"/>
     </row>
     <row r="41" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A41" s="39">
+      <c r="A41" s="38">
         <v>36</v>
       </c>
-      <c r="B41" s="49"/>
-      <c r="C41" s="50"/>
-      <c r="D41" s="50"/>
-      <c r="E41" s="50"/>
-      <c r="F41" s="50"/>
-      <c r="G41" s="50"/>
-      <c r="H41" s="50"/>
-      <c r="I41" s="50"/>
-      <c r="J41" s="50"/>
-      <c r="K41" s="50"/>
-      <c r="L41" s="50"/>
-      <c r="M41" s="50"/>
-      <c r="N41" s="51"/>
-      <c r="O41" s="51"/>
-      <c r="P41" s="51"/>
-      <c r="Q41" s="51"/>
-      <c r="R41" s="51"/>
-      <c r="S41" s="50"/>
+      <c r="B41" s="56"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
+      <c r="J41" s="57"/>
+      <c r="K41" s="57"/>
+      <c r="L41" s="57"/>
+      <c r="M41" s="57"/>
+      <c r="N41" s="58"/>
+      <c r="O41" s="58"/>
+      <c r="P41" s="58"/>
+      <c r="Q41" s="58"/>
+      <c r="R41" s="58"/>
+      <c r="S41" s="57"/>
     </row>
     <row r="42" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A42" s="39">
+      <c r="A42" s="38">
         <v>37</v>
       </c>
-      <c r="B42" s="49"/>
-      <c r="C42" s="50"/>
-      <c r="D42" s="50"/>
-      <c r="E42" s="50"/>
-      <c r="F42" s="50"/>
-      <c r="G42" s="50"/>
-      <c r="H42" s="50"/>
-      <c r="I42" s="50"/>
-      <c r="J42" s="50"/>
-      <c r="K42" s="50"/>
-      <c r="L42" s="50"/>
-      <c r="M42" s="50"/>
-      <c r="N42" s="51"/>
-      <c r="O42" s="51"/>
-      <c r="P42" s="51"/>
-      <c r="Q42" s="51"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="50"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
+      <c r="J42" s="57"/>
+      <c r="K42" s="57"/>
+      <c r="L42" s="57"/>
+      <c r="M42" s="57"/>
+      <c r="N42" s="58"/>
+      <c r="O42" s="58"/>
+      <c r="P42" s="58"/>
+      <c r="Q42" s="58"/>
+      <c r="R42" s="58"/>
+      <c r="S42" s="57"/>
     </row>
     <row r="43" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A43" s="39">
+      <c r="A43" s="38">
         <v>38</v>
       </c>
-      <c r="B43" s="49"/>
-      <c r="C43" s="50"/>
-      <c r="D43" s="50"/>
-      <c r="E43" s="50"/>
-      <c r="F43" s="50"/>
-      <c r="G43" s="50"/>
-      <c r="H43" s="50"/>
-      <c r="I43" s="50"/>
-      <c r="J43" s="50"/>
-      <c r="K43" s="50"/>
-      <c r="L43" s="50"/>
-      <c r="M43" s="50"/>
-      <c r="N43" s="51"/>
-      <c r="O43" s="51"/>
-      <c r="P43" s="51"/>
-      <c r="Q43" s="51"/>
-      <c r="R43" s="51"/>
-      <c r="S43" s="50"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
+      <c r="J43" s="57"/>
+      <c r="K43" s="57"/>
+      <c r="L43" s="57"/>
+      <c r="M43" s="57"/>
+      <c r="N43" s="58"/>
+      <c r="O43" s="58"/>
+      <c r="P43" s="58"/>
+      <c r="Q43" s="58"/>
+      <c r="R43" s="58"/>
+      <c r="S43" s="57"/>
     </row>
     <row r="44" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A44" s="39">
+      <c r="A44" s="38">
         <v>39</v>
       </c>
-      <c r="B44" s="49"/>
-      <c r="C44" s="50"/>
-      <c r="D44" s="50"/>
-      <c r="E44" s="50"/>
-      <c r="F44" s="50"/>
-      <c r="G44" s="50"/>
-      <c r="H44" s="50"/>
-      <c r="I44" s="50"/>
-      <c r="J44" s="50"/>
-      <c r="K44" s="50"/>
-      <c r="L44" s="50"/>
-      <c r="M44" s="50"/>
-      <c r="N44" s="51"/>
-      <c r="O44" s="51"/>
-      <c r="P44" s="51"/>
-      <c r="Q44" s="51"/>
-      <c r="R44" s="51"/>
-      <c r="S44" s="50"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
+      <c r="J44" s="57"/>
+      <c r="K44" s="57"/>
+      <c r="L44" s="57"/>
+      <c r="M44" s="57"/>
+      <c r="N44" s="58"/>
+      <c r="O44" s="58"/>
+      <c r="P44" s="58"/>
+      <c r="Q44" s="58"/>
+      <c r="R44" s="58"/>
+      <c r="S44" s="57"/>
     </row>
     <row r="45" ht="18.75" customHeight="1" spans="1:19">
-      <c r="A45" s="39">
+      <c r="A45" s="38">
         <v>40</v>
       </c>
-      <c r="B45" s="49"/>
-      <c r="C45" s="50"/>
-      <c r="D45" s="50"/>
-      <c r="E45" s="50"/>
-      <c r="F45" s="50"/>
-      <c r="G45" s="50"/>
-      <c r="H45" s="50"/>
-      <c r="I45" s="50"/>
-      <c r="J45" s="50"/>
-      <c r="K45" s="50"/>
-      <c r="L45" s="50"/>
-      <c r="M45" s="50"/>
-      <c r="N45" s="51"/>
-      <c r="O45" s="51"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" s="51"/>
-      <c r="R45" s="51"/>
-      <c r="S45" s="50"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="57"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="58"/>
+      <c r="O45" s="58"/>
+      <c r="P45" s="58"/>
+      <c r="Q45" s="58"/>
+      <c r="R45" s="58"/>
+      <c r="S45" s="57"/>
     </row>
     <row r="46" ht="18.75" customHeight="1" spans="1:19">
-      <c r="M46" s="50"/>
-      <c r="N46" s="51"/>
-      <c r="O46" s="51"/>
-      <c r="P46" s="51"/>
-      <c r="Q46" s="51"/>
-      <c r="R46" s="51"/>
+      <c r="M46" s="57"/>
+      <c r="N46" s="58"/>
+      <c r="O46" s="58"/>
+      <c r="P46" s="58"/>
+      <c r="Q46" s="58"/>
+      <c r="R46" s="58"/>
     </row>
     <row r="47" ht="18.75" customHeight="1" spans="1:19">
-      <c r="M47" s="50"/>
-      <c r="N47" s="51"/>
-      <c r="O47" s="51"/>
-      <c r="P47" s="51"/>
-      <c r="Q47" s="51"/>
-      <c r="R47" s="51"/>
+      <c r="M47" s="57"/>
+      <c r="N47" s="58"/>
+      <c r="O47" s="58"/>
+      <c r="P47" s="58"/>
+      <c r="Q47" s="58"/>
+      <c r="R47" s="58"/>
     </row>
     <row r="48" ht="18.75" customHeight="1" spans="1:19">
-      <c r="M48" s="50"/>
-      <c r="N48" s="51"/>
-      <c r="O48" s="51"/>
-      <c r="P48" s="51"/>
-      <c r="Q48" s="51"/>
-      <c r="R48" s="51"/>
+      <c r="M48" s="57"/>
+      <c r="N48" s="58"/>
+      <c r="O48" s="58"/>
+      <c r="P48" s="58"/>
+      <c r="Q48" s="58"/>
+      <c r="R48" s="58"/>
     </row>
     <row r="49" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M49" s="50"/>
-      <c r="N49" s="51"/>
-      <c r="O49" s="51"/>
-      <c r="P49" s="51"/>
-      <c r="Q49" s="51"/>
-      <c r="R49" s="51"/>
+      <c r="M49" s="57"/>
+      <c r="N49" s="58"/>
+      <c r="O49" s="58"/>
+      <c r="P49" s="58"/>
+      <c r="Q49" s="58"/>
+      <c r="R49" s="58"/>
     </row>
     <row r="50" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M50" s="50"/>
-      <c r="N50" s="51"/>
-      <c r="O50" s="51"/>
-      <c r="P50" s="51"/>
-      <c r="Q50" s="51"/>
-      <c r="R50" s="51"/>
+      <c r="M50" s="57"/>
+      <c r="N50" s="58"/>
+      <c r="O50" s="58"/>
+      <c r="P50" s="58"/>
+      <c r="Q50" s="58"/>
+      <c r="R50" s="58"/>
     </row>
     <row r="51" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M51" s="50"/>
-      <c r="N51" s="51"/>
-      <c r="O51" s="51"/>
-      <c r="P51" s="51"/>
-      <c r="Q51" s="51"/>
-      <c r="R51" s="51"/>
+      <c r="M51" s="57"/>
+      <c r="N51" s="58"/>
+      <c r="O51" s="58"/>
+      <c r="P51" s="58"/>
+      <c r="Q51" s="58"/>
+      <c r="R51" s="58"/>
     </row>
     <row r="52" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M52" s="50"/>
-      <c r="N52" s="51"/>
-      <c r="O52" s="51"/>
-      <c r="P52" s="51"/>
-      <c r="Q52" s="51"/>
-      <c r="R52" s="51"/>
+      <c r="M52" s="57"/>
+      <c r="N52" s="58"/>
+      <c r="O52" s="58"/>
+      <c r="P52" s="58"/>
+      <c r="Q52" s="58"/>
+      <c r="R52" s="58"/>
     </row>
     <row r="53" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M53" s="50"/>
-      <c r="N53" s="51"/>
-      <c r="O53" s="51"/>
-      <c r="P53" s="51"/>
-      <c r="Q53" s="51"/>
-      <c r="R53" s="51"/>
+      <c r="M53" s="57"/>
+      <c r="N53" s="58"/>
+      <c r="O53" s="58"/>
+      <c r="P53" s="58"/>
+      <c r="Q53" s="58"/>
+      <c r="R53" s="58"/>
     </row>
     <row r="54" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M54" s="50"/>
-      <c r="N54" s="51"/>
-      <c r="O54" s="51"/>
-      <c r="P54" s="51"/>
-      <c r="Q54" s="51"/>
-      <c r="R54" s="51"/>
+      <c r="M54" s="57"/>
+      <c r="N54" s="58"/>
+      <c r="O54" s="58"/>
+      <c r="P54" s="58"/>
+      <c r="Q54" s="58"/>
+      <c r="R54" s="58"/>
     </row>
     <row r="55" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M55" s="50"/>
-      <c r="N55" s="51"/>
-      <c r="O55" s="51"/>
-      <c r="P55" s="51"/>
-      <c r="Q55" s="51"/>
-      <c r="R55" s="51"/>
+      <c r="M55" s="57"/>
+      <c r="N55" s="58"/>
+      <c r="O55" s="58"/>
+      <c r="P55" s="58"/>
+      <c r="Q55" s="58"/>
+      <c r="R55" s="58"/>
     </row>
     <row r="56" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M56" s="50"/>
-      <c r="N56" s="51"/>
-      <c r="O56" s="51"/>
-      <c r="P56" s="51"/>
-      <c r="Q56" s="51"/>
-      <c r="R56" s="51"/>
+      <c r="M56" s="57"/>
+      <c r="N56" s="58"/>
+      <c r="O56" s="58"/>
+      <c r="P56" s="58"/>
+      <c r="Q56" s="58"/>
+      <c r="R56" s="58"/>
     </row>
     <row r="57" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M57" s="50"/>
-      <c r="N57" s="51"/>
-      <c r="O57" s="51"/>
-      <c r="P57" s="51"/>
-      <c r="Q57" s="51"/>
-      <c r="R57" s="51"/>
+      <c r="M57" s="57"/>
+      <c r="N57" s="58"/>
+      <c r="O57" s="58"/>
+      <c r="P57" s="58"/>
+      <c r="Q57" s="58"/>
+      <c r="R57" s="58"/>
     </row>
     <row r="58" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M58" s="50"/>
-      <c r="N58" s="51"/>
-      <c r="O58" s="51"/>
-      <c r="P58" s="51"/>
-      <c r="Q58" s="51"/>
-      <c r="R58" s="51"/>
+      <c r="M58" s="57"/>
+      <c r="N58" s="58"/>
+      <c r="O58" s="58"/>
+      <c r="P58" s="58"/>
+      <c r="Q58" s="58"/>
+      <c r="R58" s="58"/>
     </row>
     <row r="59" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M59" s="50"/>
-      <c r="N59" s="51"/>
-      <c r="O59" s="51"/>
-      <c r="P59" s="51"/>
-      <c r="Q59" s="51"/>
-      <c r="R59" s="51"/>
+      <c r="M59" s="57"/>
+      <c r="N59" s="58"/>
+      <c r="O59" s="58"/>
+      <c r="P59" s="58"/>
+      <c r="Q59" s="58"/>
+      <c r="R59" s="58"/>
     </row>
     <row r="60" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M60" s="50"/>
-      <c r="N60" s="51"/>
-      <c r="O60" s="51"/>
-      <c r="P60" s="51"/>
-      <c r="Q60" s="51"/>
-      <c r="R60" s="51"/>
+      <c r="M60" s="57"/>
+      <c r="N60" s="58"/>
+      <c r="O60" s="58"/>
+      <c r="P60" s="58"/>
+      <c r="Q60" s="58"/>
+      <c r="R60" s="58"/>
     </row>
     <row r="61" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M61" s="50"/>
-      <c r="N61" s="51"/>
-      <c r="O61" s="51"/>
-      <c r="P61" s="51"/>
-      <c r="Q61" s="51"/>
-      <c r="R61" s="51"/>
+      <c r="M61" s="57"/>
+      <c r="N61" s="58"/>
+      <c r="O61" s="58"/>
+      <c r="P61" s="58"/>
+      <c r="Q61" s="58"/>
+      <c r="R61" s="58"/>
     </row>
     <row r="62" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M62" s="50"/>
-      <c r="N62" s="51"/>
-      <c r="O62" s="51"/>
-      <c r="P62" s="51"/>
-      <c r="Q62" s="51"/>
-      <c r="R62" s="51"/>
+      <c r="M62" s="57"/>
+      <c r="N62" s="58"/>
+      <c r="O62" s="58"/>
+      <c r="P62" s="58"/>
+      <c r="Q62" s="58"/>
+      <c r="R62" s="58"/>
     </row>
     <row r="63" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M63" s="50"/>
-      <c r="N63" s="51"/>
-      <c r="O63" s="51"/>
-      <c r="P63" s="51"/>
-      <c r="Q63" s="51"/>
-      <c r="R63" s="51"/>
+      <c r="M63" s="57"/>
+      <c r="N63" s="58"/>
+      <c r="O63" s="58"/>
+      <c r="P63" s="58"/>
+      <c r="Q63" s="58"/>
+      <c r="R63" s="58"/>
     </row>
     <row r="64" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M64" s="50"/>
-      <c r="N64" s="51"/>
-      <c r="O64" s="51"/>
-      <c r="P64" s="51"/>
-      <c r="Q64" s="51"/>
-      <c r="R64" s="51"/>
+      <c r="M64" s="57"/>
+      <c r="N64" s="58"/>
+      <c r="O64" s="58"/>
+      <c r="P64" s="58"/>
+      <c r="Q64" s="58"/>
+      <c r="R64" s="58"/>
     </row>
     <row r="65" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M65" s="50"/>
-      <c r="N65" s="51"/>
-      <c r="O65" s="51"/>
-      <c r="P65" s="51"/>
-      <c r="Q65" s="51"/>
-      <c r="R65" s="51"/>
+      <c r="M65" s="57"/>
+      <c r="N65" s="58"/>
+      <c r="O65" s="58"/>
+      <c r="P65" s="58"/>
+      <c r="Q65" s="58"/>
+      <c r="R65" s="58"/>
     </row>
     <row r="66" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M66" s="50"/>
-      <c r="N66" s="51"/>
-      <c r="O66" s="51"/>
-      <c r="P66" s="51"/>
-      <c r="Q66" s="51"/>
-      <c r="R66" s="51"/>
+      <c r="M66" s="57"/>
+      <c r="N66" s="58"/>
+      <c r="O66" s="58"/>
+      <c r="P66" s="58"/>
+      <c r="Q66" s="58"/>
+      <c r="R66" s="58"/>
     </row>
     <row r="67" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M67" s="50"/>
-      <c r="N67" s="51"/>
-      <c r="O67" s="51"/>
-      <c r="P67" s="51"/>
-      <c r="Q67" s="51"/>
-      <c r="R67" s="51"/>
+      <c r="M67" s="57"/>
+      <c r="N67" s="58"/>
+      <c r="O67" s="58"/>
+      <c r="P67" s="58"/>
+      <c r="Q67" s="58"/>
+      <c r="R67" s="58"/>
     </row>
     <row r="68" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M68" s="50"/>
-      <c r="N68" s="51"/>
-      <c r="O68" s="51"/>
-      <c r="P68" s="51"/>
-      <c r="Q68" s="51"/>
-      <c r="R68" s="51"/>
+      <c r="M68" s="57"/>
+      <c r="N68" s="58"/>
+      <c r="O68" s="58"/>
+      <c r="P68" s="58"/>
+      <c r="Q68" s="58"/>
+      <c r="R68" s="58"/>
     </row>
     <row r="69" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M69" s="50"/>
-      <c r="N69" s="51"/>
-      <c r="O69" s="51"/>
-      <c r="P69" s="51"/>
-      <c r="Q69" s="51"/>
-      <c r="R69" s="51"/>
+      <c r="M69" s="57"/>
+      <c r="N69" s="58"/>
+      <c r="O69" s="58"/>
+      <c r="P69" s="58"/>
+      <c r="Q69" s="58"/>
+      <c r="R69" s="58"/>
     </row>
     <row r="70" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M70" s="50"/>
-      <c r="N70" s="51"/>
-      <c r="O70" s="51"/>
-      <c r="P70" s="51"/>
-      <c r="Q70" s="51"/>
-      <c r="R70" s="51"/>
+      <c r="M70" s="57"/>
+      <c r="N70" s="58"/>
+      <c r="O70" s="58"/>
+      <c r="P70" s="58"/>
+      <c r="Q70" s="58"/>
+      <c r="R70" s="58"/>
     </row>
     <row r="71" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M71" s="50"/>
-      <c r="N71" s="51"/>
-      <c r="O71" s="51"/>
-      <c r="P71" s="51"/>
-      <c r="Q71" s="51"/>
-      <c r="R71" s="51"/>
+      <c r="M71" s="57"/>
+      <c r="N71" s="58"/>
+      <c r="O71" s="58"/>
+      <c r="P71" s="58"/>
+      <c r="Q71" s="58"/>
+      <c r="R71" s="58"/>
     </row>
     <row r="72" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M72" s="50"/>
-      <c r="N72" s="51"/>
-      <c r="O72" s="51"/>
-      <c r="P72" s="51"/>
-      <c r="Q72" s="51"/>
-      <c r="R72" s="51"/>
+      <c r="M72" s="57"/>
+      <c r="N72" s="58"/>
+      <c r="O72" s="58"/>
+      <c r="P72" s="58"/>
+      <c r="Q72" s="58"/>
+      <c r="R72" s="58"/>
     </row>
     <row r="73" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M73" s="50"/>
-      <c r="N73" s="51"/>
-      <c r="O73" s="51"/>
-      <c r="P73" s="51"/>
-      <c r="Q73" s="51"/>
-      <c r="R73" s="51"/>
+      <c r="M73" s="57"/>
+      <c r="N73" s="58"/>
+      <c r="O73" s="58"/>
+      <c r="P73" s="58"/>
+      <c r="Q73" s="58"/>
+      <c r="R73" s="58"/>
     </row>
     <row r="74" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M74" s="50"/>
-      <c r="N74" s="51"/>
-      <c r="O74" s="51"/>
-      <c r="P74" s="51"/>
-      <c r="Q74" s="51"/>
-      <c r="R74" s="51"/>
+      <c r="M74" s="57"/>
+      <c r="N74" s="58"/>
+      <c r="O74" s="58"/>
+      <c r="P74" s="58"/>
+      <c r="Q74" s="58"/>
+      <c r="R74" s="58"/>
     </row>
     <row r="75" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M75" s="50"/>
-      <c r="N75" s="51"/>
-      <c r="O75" s="51"/>
-      <c r="P75" s="51"/>
-      <c r="Q75" s="51"/>
-      <c r="R75" s="51"/>
+      <c r="M75" s="57"/>
+      <c r="N75" s="58"/>
+      <c r="O75" s="58"/>
+      <c r="P75" s="58"/>
+      <c r="Q75" s="58"/>
+      <c r="R75" s="58"/>
     </row>
     <row r="76" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M76" s="50"/>
-      <c r="N76" s="51"/>
-      <c r="O76" s="51"/>
-      <c r="P76" s="51"/>
-      <c r="Q76" s="51"/>
-      <c r="R76" s="51"/>
+      <c r="M76" s="57"/>
+      <c r="N76" s="58"/>
+      <c r="O76" s="58"/>
+      <c r="P76" s="58"/>
+      <c r="Q76" s="58"/>
+      <c r="R76" s="58"/>
     </row>
     <row r="77" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M77" s="50"/>
-      <c r="N77" s="51"/>
-      <c r="O77" s="51"/>
-      <c r="P77" s="51"/>
-      <c r="Q77" s="51"/>
-      <c r="R77" s="51"/>
+      <c r="M77" s="57"/>
+      <c r="N77" s="58"/>
+      <c r="O77" s="58"/>
+      <c r="P77" s="58"/>
+      <c r="Q77" s="58"/>
+      <c r="R77" s="58"/>
     </row>
     <row r="78" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M78" s="50"/>
-      <c r="N78" s="51"/>
-      <c r="O78" s="51"/>
-      <c r="P78" s="51"/>
-      <c r="Q78" s="51"/>
-      <c r="R78" s="51"/>
+      <c r="M78" s="57"/>
+      <c r="N78" s="58"/>
+      <c r="O78" s="58"/>
+      <c r="P78" s="58"/>
+      <c r="Q78" s="58"/>
+      <c r="R78" s="58"/>
     </row>
     <row r="79" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M79" s="50"/>
-      <c r="N79" s="51"/>
-      <c r="O79" s="51"/>
-      <c r="P79" s="51"/>
-      <c r="Q79" s="51"/>
-      <c r="R79" s="51"/>
+      <c r="M79" s="57"/>
+      <c r="N79" s="58"/>
+      <c r="O79" s="58"/>
+      <c r="P79" s="58"/>
+      <c r="Q79" s="58"/>
+      <c r="R79" s="58"/>
     </row>
     <row r="80" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M80" s="50"/>
-      <c r="N80" s="51"/>
-      <c r="O80" s="51"/>
-      <c r="P80" s="51"/>
-      <c r="Q80" s="51"/>
-      <c r="R80" s="51"/>
+      <c r="M80" s="57"/>
+      <c r="N80" s="58"/>
+      <c r="O80" s="58"/>
+      <c r="P80" s="58"/>
+      <c r="Q80" s="58"/>
+      <c r="R80" s="58"/>
     </row>
     <row r="81" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M81" s="50"/>
-      <c r="N81" s="51"/>
-      <c r="O81" s="51"/>
-      <c r="P81" s="51"/>
-      <c r="Q81" s="51"/>
-      <c r="R81" s="51"/>
+      <c r="M81" s="57"/>
+      <c r="N81" s="58"/>
+      <c r="O81" s="58"/>
+      <c r="P81" s="58"/>
+      <c r="Q81" s="58"/>
+      <c r="R81" s="58"/>
     </row>
     <row r="82" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M82" s="50"/>
-      <c r="N82" s="51"/>
-      <c r="O82" s="51"/>
-      <c r="P82" s="51"/>
-      <c r="Q82" s="51"/>
-      <c r="R82" s="51"/>
+      <c r="M82" s="57"/>
+      <c r="N82" s="58"/>
+      <c r="O82" s="58"/>
+      <c r="P82" s="58"/>
+      <c r="Q82" s="58"/>
+      <c r="R82" s="58"/>
     </row>
     <row r="83" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M83" s="50"/>
-      <c r="N83" s="51"/>
-      <c r="O83" s="51"/>
-      <c r="P83" s="51"/>
-      <c r="Q83" s="51"/>
-      <c r="R83" s="51"/>
+      <c r="M83" s="57"/>
+      <c r="N83" s="58"/>
+      <c r="O83" s="58"/>
+      <c r="P83" s="58"/>
+      <c r="Q83" s="58"/>
+      <c r="R83" s="58"/>
     </row>
     <row r="84" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M84" s="50"/>
-      <c r="N84" s="51"/>
-      <c r="O84" s="51"/>
-      <c r="P84" s="51"/>
-      <c r="Q84" s="51"/>
-      <c r="R84" s="51"/>
+      <c r="M84" s="57"/>
+      <c r="N84" s="58"/>
+      <c r="O84" s="58"/>
+      <c r="P84" s="58"/>
+      <c r="Q84" s="58"/>
+      <c r="R84" s="58"/>
     </row>
     <row r="85" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M85" s="50"/>
-      <c r="N85" s="51"/>
-      <c r="O85" s="51"/>
-      <c r="P85" s="51"/>
-      <c r="Q85" s="51"/>
-      <c r="R85" s="51"/>
+      <c r="M85" s="57"/>
+      <c r="N85" s="58"/>
+      <c r="O85" s="58"/>
+      <c r="P85" s="58"/>
+      <c r="Q85" s="58"/>
+      <c r="R85" s="58"/>
     </row>
     <row r="86" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M86" s="50"/>
-      <c r="N86" s="51"/>
-      <c r="O86" s="51"/>
-      <c r="P86" s="51"/>
-      <c r="Q86" s="51"/>
-      <c r="R86" s="51"/>
+      <c r="M86" s="57"/>
+      <c r="N86" s="58"/>
+      <c r="O86" s="58"/>
+      <c r="P86" s="58"/>
+      <c r="Q86" s="58"/>
+      <c r="R86" s="58"/>
     </row>
     <row r="87" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M87" s="50"/>
+      <c r="M87" s="57"/>
     </row>
     <row r="88" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M88" s="50"/>
+      <c r="M88" s="57"/>
     </row>
     <row r="89" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M89" s="50"/>
+      <c r="M89" s="57"/>
     </row>
     <row r="90" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M90" s="50"/>
+      <c r="M90" s="57"/>
     </row>
     <row r="91" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M91" s="50"/>
+      <c r="M91" s="57"/>
     </row>
     <row r="92" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M92" s="50"/>
+      <c r="M92" s="57"/>
     </row>
     <row r="93" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M93" s="50"/>
+      <c r="M93" s="57"/>
     </row>
     <row r="94" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M94" s="50"/>
+      <c r="M94" s="57"/>
     </row>
     <row r="95" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M95" s="50"/>
+      <c r="M95" s="57"/>
     </row>
     <row r="96" ht="18.75" customHeight="1" spans="13:18">
-      <c r="M96" s="50"/>
+      <c r="M96" s="57"/>
     </row>
     <row r="97" ht="18.75" customHeight="1" spans="13:13">
-      <c r="M97" s="50"/>
+      <c r="M97" s="57"/>
     </row>
     <row r="98" ht="18.75" customHeight="1" spans="13:13">
-      <c r="M98" s="50"/>
+      <c r="M98" s="57"/>
     </row>
     <row r="99" ht="18.75" customHeight="1" spans="13:13">
-      <c r="M99" s="50"/>
+      <c r="M99" s="57"/>
     </row>
     <row r="100" ht="18.75" customHeight="1" spans="13:13">
-      <c r="M100" s="50"/>
+      <c r="M100" s="57"/>
     </row>
     <row r="101" ht="18.75" customHeight="1" spans="13:13">
-      <c r="M101" s="50"/>
+      <c r="M101" s="57"/>
     </row>
     <row r="102" ht="18.75" customHeight="1" spans="13:13">
-      <c r="M102" s="50"/>
+      <c r="M102" s="57"/>
     </row>
     <row r="103" ht="18.75" customHeight="1" spans="13:13">
-      <c r="M103" s="50"/>
+      <c r="M103" s="57"/>
     </row>
     <row r="104" ht="18.75" customHeight="1" spans="13:13">
-      <c r="M104" s="50"/>
+      <c r="M104" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="29">
@@ -3256,22 +3522,22 @@
     <mergeCell ref="I15:I16"/>
   </mergeCells>
   <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14 M9:M10 M18:M104">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M9:M10 M19:M104">
       <formula1>"新增,报废更新"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N14 N9:N10 N18:N86">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="N9:N10 N19:N86">
       <formula1>"单排,双排"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O14 O9:O10 O18:O86">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="O9:O10 O19:O86">
       <formula1>"两驱,四驱"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P14 P9:P10 P18:P86">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="P9:P10 P19:P86">
       <formula1>"柴油,汽油,新能源,混动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q14 Q9:Q10 Q18:Q86">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q9:Q10 Q19:Q86">
       <formula1>"手动,自动"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R14 R9:R10 R18:R86">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R9:R10 R19:R86">
       <formula1>"栏板,厢式"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3299,7 +3565,7 @@
   <sheetData>
     <row r="1" ht="25.5" spans="1:13">
       <c r="A1" s="2" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
@@ -3310,7 +3576,7 @@
     </row>
     <row r="2" ht="78" customHeight="1" spans="1:13">
       <c r="A2" s="4" t="s">
-        <v>16</v>
+        <v>78</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -3321,7 +3587,7 @@
     </row>
     <row r="3" s="1" customFormat="1" ht="20" customHeight="1" spans="1:13">
       <c r="A3" s="5" t="s">
-        <v>17</v>
+        <v>79</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="5"/>
@@ -3342,30 +3608,30 @@
     </row>
     <row r="4" ht="18.75" spans="1:13">
       <c r="A4" s="9" t="s">
-        <v>18</v>
+        <v>80</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>19</v>
+        <v>81</v>
       </c>
       <c r="C4" s="11" t="s">
         <v>6</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>20</v>
+        <v>83</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>21</v>
+        <v>84</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>22</v>
+        <v>85</v>
       </c>
     </row>
     <row r="5" ht="18.75" spans="1:13">
       <c r="A5" s="12" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="B5" s="13">
         <v>5</v>
@@ -3386,7 +3652,7 @@
     </row>
     <row r="6" ht="18.75" customHeight="1" spans="1:13">
       <c r="A6" s="12" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="B6" s="15">
         <v>222</v>
@@ -3407,7 +3673,7 @@
     </row>
     <row r="7" ht="18.75" customHeight="1" spans="1:13">
       <c r="A7" s="12" t="s">
-        <v>25</v>
+        <v>88</v>
       </c>
       <c r="B7" s="17">
         <v>333</v>
@@ -3428,7 +3694,7 @@
     </row>
     <row r="8" ht="18.75" customHeight="1" spans="1:13">
       <c r="A8" s="12" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="B8" s="15">
         <v>222</v>
@@ -3449,7 +3715,7 @@
     </row>
     <row r="9" ht="37.5" customHeight="1" spans="1:13">
       <c r="A9" s="12" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="B9" s="17">
         <v>333</v>
@@ -3470,7 +3736,7 @@
     </row>
     <row r="10" ht="37.5" customHeight="1" spans="1:13">
       <c r="A10" s="12" t="s">
-        <v>28</v>
+        <v>91</v>
       </c>
       <c r="B10" s="15">
         <v>222</v>
@@ -3492,7 +3758,7 @@
     </row>
     <row r="11" ht="18.75" customHeight="1" spans="1:13">
       <c r="A11" s="12" t="s">
-        <v>29</v>
+        <v>92</v>
       </c>
       <c r="B11" s="17">
         <v>333</v>
@@ -3513,7 +3779,7 @@
     </row>
     <row r="12" ht="18.75" customHeight="1" spans="1:13">
       <c r="A12" s="12" t="s">
-        <v>30</v>
+        <v>93</v>
       </c>
       <c r="B12" s="15">
         <v>222</v>
@@ -3534,7 +3800,7 @@
     </row>
     <row r="13" ht="37.5" customHeight="1" spans="1:13">
       <c r="A13" s="12" t="s">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="B13" s="17">
         <v>333</v>
@@ -3555,7 +3821,7 @@
     </row>
     <row r="14" ht="18.75" customHeight="1" spans="1:13">
       <c r="A14" s="12" t="s">
-        <v>32</v>
+        <v>95</v>
       </c>
       <c r="B14" s="15">
         <v>222</v>
@@ -3576,7 +3842,7 @@
     </row>
     <row r="15" ht="18.75" customHeight="1" spans="1:13">
       <c r="A15" s="12" t="s">
-        <v>33</v>
+        <v>96</v>
       </c>
       <c r="B15" s="17">
         <v>333</v>
@@ -3597,7 +3863,7 @@
     </row>
     <row r="16" ht="18.75" customHeight="1" spans="1:13">
       <c r="A16" s="12" t="s">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="B16" s="15">
         <v>222</v>
@@ -3618,7 +3884,7 @@
     </row>
     <row r="17" ht="18.75" customHeight="1" spans="1:7">
       <c r="A17" s="12" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="B17" s="17">
         <v>333</v>
@@ -3639,7 +3905,7 @@
     </row>
     <row r="18" ht="18.75" customHeight="1" spans="1:7">
       <c r="A18" s="12" t="s">
-        <v>36</v>
+        <v>99</v>
       </c>
       <c r="B18" s="17">
         <v>333</v>
@@ -3660,7 +3926,7 @@
     </row>
     <row r="19" ht="18.75" customHeight="1" spans="1:7">
       <c r="A19" s="12" t="s">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="B19" s="15">
         <v>222</v>
